--- a/data/trans_dic/P55$familiarvive-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiarvive-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 26,21</t>
+          <t>4,9; 27,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 26,76</t>
+          <t>2,48; 22,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 32,25</t>
+          <t>6,36; 32,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 24,86</t>
+          <t>7,46; 24,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,11; 25,18</t>
+          <t>8,34; 25,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,88; 40,34</t>
+          <t>19,15; 41,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,73; 30,65</t>
+          <t>11,92; 31,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,75; 27,72</t>
+          <t>15,58; 29,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,3; 22,64</t>
+          <t>8,4; 22,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,31; 29,0</t>
+          <t>14,17; 30,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,25; 27,68</t>
+          <t>12,02; 27,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,48; 23,79</t>
+          <t>14,03; 24,93</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 25,59</t>
+          <t>9,83; 25,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,2; 30,55</t>
+          <t>13,47; 31,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,29; 22,63</t>
+          <t>9,07; 23,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 14,54</t>
+          <t>5,26; 13,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,91; 45,19</t>
+          <t>28,86; 45,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,34; 35,92</t>
+          <t>23,34; 36,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,99; 36,37</t>
+          <t>22,6; 37,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,31; 23,51</t>
+          <t>16,43; 23,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,49; 35,56</t>
+          <t>24,17; 36,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,72; 32,31</t>
+          <t>21,85; 31,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,1; 30,62</t>
+          <t>19,22; 30,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,97; 19,93</t>
+          <t>13,81; 19,54</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,94; 22,62</t>
+          <t>9,86; 22,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,84; 25,97</t>
+          <t>12,08; 26,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,96; 22,16</t>
+          <t>9,5; 21,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 14,78</t>
+          <t>7,33; 15,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,37; 37,07</t>
+          <t>24,39; 36,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,57; 34,51</t>
+          <t>23,66; 35,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,8; 32,5</t>
+          <t>21,34; 33,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,17; 23,44</t>
+          <t>16,98; 23,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,75; 30,25</t>
+          <t>20,76; 30,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,27; 29,66</t>
+          <t>21,13; 29,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,81; 27,81</t>
+          <t>18,6; 27,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,67; 19,82</t>
+          <t>15,06; 20,0</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7046</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>17344</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22264</t>
+          <t>25626</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1846; 10953</t>
+          <t>2048; 11297</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2040; 12163</t>
+          <t>1126; 10374</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1946; 10106</t>
+          <t>1992; 10051</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3621; 12533</t>
+          <t>4109; 13691</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5489; 17034</t>
+          <t>5646; 17116</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13162; 28123</t>
+          <t>13350; 29004</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9639; 25174</t>
+          <t>9791; 25838</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10775; 20243</t>
+          <t>12547; 23356</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10183; 24777</t>
+          <t>9198; 24718</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16477; 33399</t>
+          <t>16315; 34857</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13896; 31410</t>
+          <t>13640; 31359</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16636; 29370</t>
+          <t>19024; 33799</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50445</t>
+          <t>54573</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>64776</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8475; 21697</t>
+          <t>8336; 21834</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13295; 30772</t>
+          <t>13570; 31903</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8373; 20390</t>
+          <t>8178; 21260</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6004; 15504</t>
+          <t>5997; 15772</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47198; 73782</t>
+          <t>47122; 73619</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46882; 75369</t>
+          <t>48962; 76980</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40734; 67362</t>
+          <t>41853; 69437</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41616; 59995</t>
+          <t>45458; 65283</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58272; 88200</t>
+          <t>59957; 89566</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67460; 100338</t>
+          <t>67858; 98381</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52597; 84310</t>
+          <t>52931; 83142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50554; 72108</t>
+          <t>53969; 76371</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65663</t>
+          <t>71918</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82643</t>
+          <t>90402</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12583; 28630</t>
+          <t>12479; 28676</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17303; 37958</t>
+          <t>17651; 38661</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12101; 26920</t>
+          <t>11535; 26314</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11073; 23212</t>
+          <t>12401; 25873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56279; 85605</t>
+          <t>56317; 84259</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65884; 96460</t>
+          <t>66146; 98151</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55599; 86891</t>
+          <t>57053; 88563</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56376; 76944</t>
+          <t>60645; 84124</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>74176; 108128</t>
+          <t>74223; 108590</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90556; 126274</t>
+          <t>89947; 126573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73146; 108127</t>
+          <t>72307; 107990</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71176; 96198</t>
+          <t>79288; 105282</t>
         </is>
       </c>
     </row>
